--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-17.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>1.85</v>
@@ -1401,184 +1401,184 @@
         <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
         <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
         <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
         <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -2130,227 +2130,227 @@
         <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
         <v>440</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
         <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G14" t="n">
         <v>2.02</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
         <v>1.7</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>1.66</v>
       </c>
       <c r="H15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I15" t="n">
         <v>5.6</v>
       </c>
-      <c r="I15" t="n">
-        <v>5.7</v>
-      </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
         <v>4.7</v>
@@ -4288,7 +4288,7 @@
         <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
         <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE15" t="n">
         <v>55</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
         <v>3.85</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>4.6</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="I19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="G20" t="n">
         <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J20" t="n">
         <v>3.6</v>
@@ -5462,7 +5462,7 @@
         <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="H21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H23" t="n">
         <v>2.28</v>
@@ -6203,10 +6203,10 @@
         <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q24" t="n">
         <v>1.43</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.89</v>
       </c>
       <c r="G25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H25" t="n">
         <v>3.8</v>
@@ -6714,7 +6714,7 @@
         <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>3.05</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
         <v>2.92</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
         <v>2.14</v>
@@ -7216,7 +7216,7 @@
         <v>3.4</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J27" t="n">
         <v>3.6</v>
@@ -7240,7 +7240,7 @@
         <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -7464,16 +7464,16 @@
         <v>1.84</v>
       </c>
       <c r="G28" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H28" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="I28" t="n">
         <v>670</v>
       </c>
       <c r="J28" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="K28" t="n">
         <v>100</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H30" t="n">
         <v>2.38</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>3.45</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="G34" t="n">
         <v>2.2</v>
       </c>
       <c r="H34" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
         <v>1.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -9239,13 +9239,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
         <v>2.24</v>
       </c>
       <c r="H35" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="I35" t="n">
         <v>4.4</v>
@@ -9254,7 +9254,7 @@
         <v>1.01</v>
       </c>
       <c r="K35" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -9493,16 +9493,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G36" t="n">
         <v>1.99</v>
       </c>
       <c r="H36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>3.6</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
         <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -10007,13 +10007,13 @@
         <v>4.1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I38" t="n">
         <v>1.98</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K38" t="n">
         <v>4.2</v>
@@ -10082,7 +10082,7 @@
         <v>38</v>
       </c>
       <c r="AG38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH38" t="n">
         <v>17.5</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1.5</v>
       </c>
       <c r="J39" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
         <v>3.4</v>
       </c>
       <c r="H40" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I40" t="n">
         <v>2.28</v>
@@ -10563,10 +10563,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
         <v>16.5</v>
@@ -10617,16 +10617,16 @@
         <v>13.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR40" t="n">
         <v>15</v>
       </c>
       <c r="AS40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT40" t="n">
         <v>15</v>
@@ -10656,7 +10656,7 @@
         <v>29</v>
       </c>
       <c r="BC40" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BD40" t="n">
         <v>34</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
         <v>3.85</v>
       </c>
       <c r="K41" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -10796,7 +10796,7 @@
         <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R41" t="n">
         <v>1.38</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -11274,19 +11274,19 @@
         <v>1.78</v>
       </c>
       <c r="G43" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H43" t="n">
         <v>5.4</v>
       </c>
       <c r="I43" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K43" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -11528,13 +11528,13 @@
         <v>1.04</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H44" t="n">
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -11779,16 +11779,16 @@
         </is>
       </c>
       <c r="F45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G45" t="n">
         <v>1.77</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.78</v>
       </c>
       <c r="H45" t="n">
         <v>4.6</v>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>4.5</v>
@@ -11806,7 +11806,7 @@
         <v>4.8</v>
       </c>
       <c r="O45" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P45" t="n">
         <v>2.32</v>
@@ -11857,7 +11857,7 @@
         <v>65</v>
       </c>
       <c r="AF45" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG45" t="n">
         <v>9.800000000000001</v>
@@ -11869,31 +11869,31 @@
         <v>65</v>
       </c>
       <c r="AJ45" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK45" t="n">
         <v>17.5</v>
       </c>
       <c r="AL45" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM45" t="n">
         <v>85</v>
       </c>
       <c r="AN45" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO45" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP45" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ45" t="n">
         <v>17.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS45" t="n">
         <v>38</v>
@@ -11905,10 +11905,10 @@
         <v>9</v>
       </c>
       <c r="AV45" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AX45" t="n">
         <v>10.5</v>
@@ -11923,7 +11923,7 @@
         <v>28</v>
       </c>
       <c r="BB45" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC45" t="n">
         <v>15.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -12544,19 +12544,19 @@
         <v>1.53</v>
       </c>
       <c r="G48" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H48" t="n">
         <v>6.4</v>
       </c>
       <c r="I48" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J48" t="n">
         <v>4.2</v>
       </c>
       <c r="K48" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>2.56</v>
       </c>
       <c r="J49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K49" t="n">
         <v>3.75</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
         <v>2.3</v>
       </c>
       <c r="I50" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J50" t="n">
         <v>3.25</v>
@@ -13082,7 +13082,7 @@
         <v>1.86</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G51" t="n">
         <v>3.8</v>
@@ -13312,7 +13312,7 @@
         <v>2.14</v>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J51" t="n">
         <v>3.35</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="G53" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H53" t="n">
         <v>3.1</v>
@@ -13826,7 +13826,7 @@
         <v>3.7</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -13841,7 +13841,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q53" t="n">
         <v>1.54</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -14573,16 +14573,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G56" t="n">
         <v>1.63</v>
       </c>
       <c r="H56" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I56" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J56" t="n">
         <v>4.5</v>
@@ -14615,10 +14615,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U56" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -14627,7 +14627,7 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y56" t="n">
         <v>30</v>
@@ -14663,7 +14663,7 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AK56" t="n">
         <v>970</v>
@@ -14678,7 +14678,7 @@
         <v>7.4</v>
       </c>
       <c r="AO56" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP56" t="n">
         <v>18.5</v>
@@ -14732,7 +14732,7 @@
         <v>5</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH56" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -14827,13 +14827,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="G57" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I57" t="n">
         <v>1.83</v>
@@ -14842,7 +14842,7 @@
         <v>3.6</v>
       </c>
       <c r="K57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -15335,22 +15335,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H59" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I59" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J59" t="n">
         <v>3.75</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
         <v>2.2</v>
       </c>
       <c r="G60" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H60" t="n">
         <v>3.35</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G61" t="n">
         <v>2.24</v>
@@ -15855,7 +15855,7 @@
         <v>3.4</v>
       </c>
       <c r="J61" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K61" t="n">
         <v>4</v>
@@ -15921,13 +15921,13 @@
         <v>32</v>
       </c>
       <c r="AF61" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG61" t="n">
         <v>11.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AI61" t="n">
         <v>34</v>
@@ -15936,7 +15936,7 @@
         <v>29</v>
       </c>
       <c r="AK61" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL61" t="n">
         <v>26</v>
@@ -15966,7 +15966,7 @@
         <v>14.5</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV61" t="n">
         <v>13</v>
@@ -15996,13 +15996,13 @@
         <v>23</v>
       </c>
       <c r="BE61" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF61" t="n">
         <v>9</v>
       </c>
       <c r="BG61" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -16100,19 +16100,19 @@
         <v>3.15</v>
       </c>
       <c r="G62" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H62" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I62" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J62" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K62" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -16351,22 +16351,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H63" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I63" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J63" t="n">
         <v>3.45</v>
       </c>
       <c r="K63" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -16381,10 +16381,10 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
         <v>1.84</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -17367,22 +17367,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G67" t="n">
         <v>3.85</v>
       </c>
       <c r="H67" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J67" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K67" t="n">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -17875,22 +17875,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="H69" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="I69" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K69" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -17905,10 +17905,10 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -18159,10 +18159,10 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -18637,22 +18637,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G72" t="n">
         <v>3.45</v>
       </c>
       <c r="H72" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I72" t="n">
         <v>3.25</v>
       </c>
       <c r="J72" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="K72" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -18891,16 +18891,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="H73" t="n">
         <v>4.5</v>
       </c>
       <c r="I73" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>3.6</v>
@@ -18921,10 +18921,10 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -19145,19 +19145,19 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G74" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="H74" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J74" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I74" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J74" t="n">
-        <v>3.1</v>
       </c>
       <c r="K74" t="n">
         <v>3.7</v>
@@ -19175,7 +19175,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q74" t="n">
         <v>2.24</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G75" t="n">
         <v>2.88</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -20167,7 +20167,7 @@
         <v>1000</v>
       </c>
       <c r="H78" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I78" t="n">
         <v>2.18</v>
@@ -20191,7 +20191,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q78" t="n">
         <v>1.94</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -21180,10 +21180,10 @@
         <v>1.99</v>
       </c>
       <c r="G82" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="H82" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I82" t="n">
         <v>6.2</v>
@@ -21192,7 +21192,7 @@
         <v>3</v>
       </c>
       <c r="K82" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -21207,10 +21207,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -21688,10 +21688,10 @@
         <v>1.99</v>
       </c>
       <c r="G84" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H84" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I84" t="n">
         <v>4.5</v>
@@ -21700,7 +21700,7 @@
         <v>3.35</v>
       </c>
       <c r="K84" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -21718,7 +21718,7 @@
         <v>1.78</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="G85" t="n">
         <v>1.83</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="CB86" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -22447,7 +22447,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G87" t="n">
         <v>2.7</v>
@@ -22462,7 +22462,7 @@
         <v>2.88</v>
       </c>
       <c r="K87" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -22477,10 +22477,10 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="CB87" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -22707,16 +22707,16 @@
         <v>1.94</v>
       </c>
       <c r="H88" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I88" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J88" t="n">
-        <v>2.06</v>
+        <v>3.15</v>
       </c>
       <c r="K88" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="CB88" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -22955,22 +22955,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G89" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H89" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="I89" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="J89" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="K89" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -22985,7 +22985,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q89" t="n">
         <v>1.96</v>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="CB89" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G90" t="n">
         <v>3.7</v>
@@ -23224,7 +23224,7 @@
         <v>3.3</v>
       </c>
       <c r="K90" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -23239,7 +23239,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q90" t="n">
         <v>2.18</v>
@@ -23432,7 +23432,7 @@
       </c>
       <c r="CB90" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -23463,7 +23463,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G91" t="n">
         <v>3.25</v>
@@ -23475,10 +23475,10 @@
         <v>4.1</v>
       </c>
       <c r="J91" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="K91" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -23686,7 +23686,7 @@
       </c>
       <c r="CB91" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -23717,13 +23717,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G92" t="n">
         <v>3.7</v>
       </c>
       <c r="H92" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I92" t="n">
         <v>2.6</v>
@@ -23732,7 +23732,7 @@
         <v>3.25</v>
       </c>
       <c r="K92" t="n">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -23747,10 +23747,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -23777,10 +23777,10 @@
         <v>10.5</v>
       </c>
       <c r="Z92" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA92" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB92" t="n">
         <v>13</v>
@@ -23792,13 +23792,13 @@
         <v>970</v>
       </c>
       <c r="AE92" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF92" t="n">
         <v>28</v>
       </c>
       <c r="AG92" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH92" t="n">
         <v>25</v>
@@ -23819,7 +23819,7 @@
         <v>170</v>
       </c>
       <c r="AN92" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO92" t="n">
         <v>38</v>
@@ -23828,16 +23828,16 @@
         <v>7.6</v>
       </c>
       <c r="AQ92" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR92" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS92" t="n">
         <v>3.95</v>
       </c>
       <c r="AT92" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU92" t="n">
         <v>5.6</v>
@@ -23852,10 +23852,10 @@
         <v>16.5</v>
       </c>
       <c r="AY92" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ92" t="n">
-        <v>3.7</v>
+        <v>14.5</v>
       </c>
       <c r="BA92" t="n">
         <v>4</v>
@@ -23873,10 +23873,10 @@
         <v>4.2</v>
       </c>
       <c r="BF92" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG92" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BH92" t="n">
         <v>0</v>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="CB92" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
@@ -23974,19 +23974,19 @@
         <v>2.02</v>
       </c>
       <c r="G93" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H93" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I93" t="n">
         <v>4.5</v>
       </c>
       <c r="J93" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K93" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="CB93" t="inlineStr">
         <is>
-          <t>2026-05-15 04:00:23</t>
+          <t>2026-05-15 06:34:17</t>
         </is>
       </c>
     </row>
